--- a/internal/test/excels/struct.xlsx
+++ b/internal/test/excels/struct.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13180"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="|Struct_0" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>Tag</t>
   </si>
@@ -55,6 +55,21 @@
   </si>
   <si>
     <t>道具数量</t>
+  </si>
+  <si>
+    <t>itemTypePair</t>
+  </si>
+  <si>
+    <t>itemType:ItemType:"道具类型", value:int32:"数值"</t>
+  </si>
+  <si>
+    <t>道具类型对</t>
+  </si>
+  <si>
+    <t>itemTypeList</t>
+  </si>
+  <si>
+    <t>list:[]ItemType:""</t>
   </si>
   <si>
     <t>itemCountArray</t>
@@ -962,6 +977,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1214,8 +1236,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.5384615384615" customWidth="1"/>
     <col min="2" max="4" width="62.1538461538462" customWidth="1"/>
@@ -1252,6 +1274,25 @@
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1290,13 +1331,13 @@
     </row>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/internal/test/excels/struct.xlsx
+++ b/internal/test/excels/struct.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowWidth="29100" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="|Struct_0" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Tag</t>
   </si>
@@ -70,6 +70,21 @@
   </si>
   <si>
     <t>list:[]ItemType:""</t>
+  </si>
+  <si>
+    <t>testMap</t>
+  </si>
+  <si>
+    <t>m:map[string]int32:"test"</t>
+  </si>
+  <si>
+    <t>itemCountMap</t>
+  </si>
+  <si>
+    <t>m:map[int32]itemCount:"test"</t>
+  </si>
+  <si>
+    <t>link=m,k1:Item.ID</t>
   </si>
   <si>
     <t>itemCountArray</t>
@@ -1236,8 +1251,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.5384615384615" customWidth="1"/>
     <col min="2" max="4" width="62.1538461538462" customWidth="1"/>
@@ -1293,6 +1308,25 @@
       </c>
       <c r="C4" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1331,13 +1365,13 @@
     </row>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/internal/test/excels/struct.xlsx
+++ b/internal/test/excels/struct.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13420"/>
+    <workbookView windowWidth="29100" windowHeight="13420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="|Struct_0" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Tag</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>c/s</t>
   </si>
   <si>
     <t>itemCount</t>
@@ -1277,56 +1280,70 @@
       </c>
     </row>
     <row r="2" ht="17" spans="1:5">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:5">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
+    <row r="4" ht="17" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:3">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
+    <row r="5" ht="17" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:3">
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
+    <row r="6" ht="17" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1363,15 +1380,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:5">
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
